--- a/test_subjects_faculty.xlsx
+++ b/test_subjects_faculty.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,101 +461,101 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dr. Rao</t>
+          <t>Dr. Patel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CS-B</t>
+          <t>CS-A</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dr. Singh</t>
+          <t>Prof. Reddy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CS-C</t>
+          <t>CS-A</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>English</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dr. Singh</t>
+          <t>Dr. Sharma</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EC-A</t>
+          <t>CS-A</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>CS Lab</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dr. Singh</t>
+          <t>Prof. Reddy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EC-B</t>
+          <t>CS-A</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dr. Patel</t>
+          <t>Dr. Singh</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CS-A</t>
+          <t>CS-B</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -566,7 +566,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dr. Patel</t>
+          <t>Dr. Mehta</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -581,17 +581,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Computer Science</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dr. Patel</t>
+          <t>Prof. Reddy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CS-C</t>
+          <t>CS-B</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -601,37 +601,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>English</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dr. Patel</t>
+          <t>Dr. Sharma</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EC-A</t>
+          <t>CS-B</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Physics Lab</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dr. Patel</t>
+          <t>Dr. Mehta</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>EC-B</t>
+          <t>CS-B</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -641,37 +641,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prof. Kumar</t>
+          <t>Dr. Rao</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CS-A</t>
+          <t>EC-A</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Prof. Kumar</t>
+          <t>Dr. Kumar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CS-B</t>
+          <t>EC-A</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -681,12 +681,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chemistry</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prof. Kumar</t>
+          <t>Dr. Patel</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CS-A</t>
+          <t>EC-A</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -721,32 +721,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Physics Lab</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dr. Sharma</t>
+          <t>Dr. Patel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CS-C</t>
+          <t>EC-A</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dr. Sharma</t>
+          <t>Dr. Singh</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -755,23 +755,23 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Prof. Reddy</t>
+          <t>Dr. Kumar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CS-A</t>
+          <t>EC-B</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -781,17 +781,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Prof. Reddy</t>
+          <t>Dr. Mehta</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CS-B</t>
+          <t>EC-B</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -801,140 +801,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>English</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Prof. Reddy</t>
+          <t>Dr. Sharma</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CS-C</t>
+          <t>EC-B</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>CS Lab</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dr. Sharma</t>
+          <t>Prof. Reddy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EC-A</t>
+          <t>EC-B</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Dr. Sharma</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>EC-B</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Physics Lab</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Dr. Patel</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CS-A</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Physics Lab</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Dr. Patel</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>EC-A</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>CS Lab</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Prof. Reddy</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CS-B</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CS Lab</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Prof. Reddy</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CS-C</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
         <v>3</v>
       </c>
     </row>

--- a/test_subjects_faculty.xlsx
+++ b/test_subjects_faculty.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="subjects_faculty" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,405 +437,1114 @@
           <t>hours_per_week</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Engineering Mathematics I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dr. Rao</t>
+          <t>Prof Y1A-1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CS-A</t>
+          <t>Y1-CS-A</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dr. Patel</t>
+          <t>Prof Y1A-2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CS-A</t>
+          <t>Y1-CS-A</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Engineering Physics</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prof. Reddy</t>
+          <t>Prof Y1A-3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CS-A</t>
+          <t>Y1-CS-A</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Communication Skills</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dr. Sharma</t>
+          <t>Prof Y1A-4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CS-A</t>
+          <t>Y1-CS-A</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CS Lab</t>
+          <t>Programming Lab</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prof. Reddy</t>
+          <t>Prof Y1A-5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CS-A</t>
+          <t>Y1-CS-A</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Physics Lab</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dr. Singh</t>
+          <t>Prof Y1A-6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CS-B</t>
+          <t>Y1-CS-A</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Engineering Mathematics I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dr. Mehta</t>
+          <t>Prof Y1B-1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CS-B</t>
+          <t>Y1-CS-B</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Programming Fundamentals</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prof. Reddy</t>
+          <t>Prof Y1B-2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CS-B</t>
+          <t>Y1-CS-B</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Engineering Physics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dr. Sharma</t>
+          <t>Prof Y1B-3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CS-B</t>
+          <t>Y1-CS-B</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Physics Lab</t>
+          <t>Communication Skills</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dr. Mehta</t>
+          <t>Prof Y1B-4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CS-B</t>
+          <t>Y1-CS-B</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Programming Lab</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dr. Rao</t>
+          <t>Prof Y1B-5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EC-A</t>
+          <t>Y1-CS-B</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Physics Lab</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dr. Kumar</t>
+          <t>Prof Y1B-6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EC-A</t>
+          <t>Y1-CS-B</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Discrete Mathematics</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dr. Patel</t>
+          <t>Prof Y2A-1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EC-A</t>
+          <t>Y2-CS-A</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dr. Sharma</t>
+          <t>Prof Y2A-2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EC-A</t>
+          <t>Y2-CS-A</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Physics Lab</t>
+          <t>Digital Systems</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dr. Patel</t>
+          <t>Prof Y2A-3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EC-A</t>
+          <t>Y2-CS-A</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Database Fundamentals</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dr. Singh</t>
+          <t>Prof Y2A-4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>EC-B</t>
+          <t>Y2-CS-A</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Data Structures Lab</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dr. Kumar</t>
+          <t>Prof Y2A-5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>EC-B</t>
+          <t>Y2-CS-A</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>Database Lab</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dr. Mehta</t>
+          <t>Prof Y2A-6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EC-B</t>
+          <t>Y2-CS-A</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Discrete Mathematics</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dr. Sharma</t>
+          <t>Prof Y2B-1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EC-B</t>
+          <t>Y2-CS-B</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CS Lab</t>
+          <t>Data Structures</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Prof. Reddy</t>
+          <t>Prof Y2B-2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EC-B</t>
+          <t>Y2-CS-B</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Digital Systems</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Prof Y2B-3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Y2-CS-B</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Database Fundamentals</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Prof Y2B-4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Y2-CS-B</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Structures Lab</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Prof Y2B-5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Y2-CS-B</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Database Lab</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Prof Y2B-6</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Y2-CS-B</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Operating Systems</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Prof Y3A-1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Y3-CS-A</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Prof Y3A-2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Y3-CS-A</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Prof Y3A-3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Y3-CS-A</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Web Technologies</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Prof Y3A-4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Y3-CS-A</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Operating Systems Lab</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Prof Y3A-5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Y3-CS-A</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Networks Lab</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Prof Y3A-6</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Y3-CS-A</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Operating Systems</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Prof Y3B-1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Y3-CS-B</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Computer Networks</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Prof Y3B-2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Y3-CS-B</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineering</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Prof Y3B-3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Y3-CS-B</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Web Technologies</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Prof Y3B-4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Y3-CS-B</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Operating Systems Lab</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Prof Y3B-5</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Y3-CS-B</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Networks Lab</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Prof Y3B-6</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Y3-CS-B</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Prof Y4A-1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Y4-CS-A</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Prof Y4A-2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Y4-CS-A</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Information Security</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Prof Y4A-3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Y4-CS-A</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Project Management</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Prof Y4A-4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Y4-CS-A</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ML Lab</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Prof Y4A-5</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Y4-CS-A</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Cloud Lab</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Prof Y4A-6</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Y4-CS-A</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Prof Y4B-1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Y4-CS-B</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cloud Computing</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Prof Y4B-2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Y4-CS-B</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Information Security</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Prof Y4B-3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Y4-CS-B</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Project Management</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Prof Y4B-4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Y4-CS-B</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ML Lab</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Prof Y4B-5</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Y4-CS-B</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Cloud Lab</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Prof Y4B-6</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Y4-CS-B</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
